--- a/연구코드/data/강남/metadata/강남_DLO_Results_Unique.xlsx
+++ b/연구코드/data/강남/metadata/강남_DLO_Results_Unique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhjun\OneDrive\Desktop\2026-1_Study\연구코드\data\강남\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22259EF8-F51B-4286-9483-EDDB6E9ED026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CA3ABA-44D5-4997-B2D4-D735493E5FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="2160" windowWidth="24075" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata1" sheetId="1" r:id="rId1"/>
@@ -882,7 +882,9 @@
       <c r="I3" s="3">
         <v>6</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7">
+        <v>18.86</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
